--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -26945,21 +26933,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-19 to 2026-03-22 | Publication days: 307</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -26967,22 +26955,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1525"/>
+  <dimension ref="A1:E1526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26909,6 +26909,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1525" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr"/>
+      <c r="C1526" t="n">
+        <v>-2.714285714285714</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1526" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26942,7 +26959,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-22 | Publication days: 307</t>
+          <t>Coverage: 2022-01-19 to 2026-03-23 | Publication days: 307</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1526"/>
+  <dimension ref="A1:E1527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26926,6 +26926,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1526" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr"/>
+      <c r="C1527" t="n">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1527" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26959,7 +26976,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-23 | Publication days: 307</t>
+          <t>Coverage: 2022-01-19 to 2026-03-24 | Publication days: 307</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1527"/>
+  <dimension ref="A1:E1528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26943,6 +26943,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1527" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr"/>
+      <c r="C1528" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1528" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26976,7 +26993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-24 | Publication days: 307</t>
+          <t>Coverage: 2022-01-19 to 2026-03-25 | Publication days: 307</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -26918,7 +26918,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B1526" t="inlineStr"/>
+      <c r="B1526" t="n">
+        <v>-3</v>
+      </c>
       <c r="C1526" t="n">
         <v>-2.714285714285714</v>
       </c>
@@ -26926,7 +26928,7 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1526" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1527">
@@ -26935,7 +26937,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1527" t="inlineStr"/>
+      <c r="B1527" t="n">
+        <v>-3</v>
+      </c>
       <c r="C1527" t="n">
         <v>-2.857142857142857</v>
       </c>
@@ -26943,7 +26947,7 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1527" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1528">
@@ -26993,7 +26997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-25 | Publication days: 307</t>
+          <t>Coverage: 2022-01-19 to 2026-03-25 | Publication days: 309</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -26988,21 +27000,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-19 to 2026-03-25 | Publication days: 309</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27010,22 +27022,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1528"/>
+  <dimension ref="A1:E1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -26976,6 +26964,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1528" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr"/>
+      <c r="C1529" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1529" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27000,21 +27005,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-19 to 2026-03-25 | Publication days: 309</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-19 to 2026-03-26 | Publication days: 309</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27022,22 +27027,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27005,21 +27017,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-19 to 2026-03-26 | Publication days: 309</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27027,22 +27039,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -27017,21 +27005,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-01-19 to 2026-03-26 | Publication days: 309</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27039,22 +27027,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1529"/>
+  <dimension ref="A1:E1530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -26993,6 +26981,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1529" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr"/>
+      <c r="C1530" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1530" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27017,21 +27022,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Spain WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-01-19 to 2026-03-26 | Publication days: 309</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-01-19 to 2026-03-27 | Publication days: 309</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -27039,22 +27044,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1530"/>
+  <dimension ref="A1:E1531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26998,6 +26998,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1530" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr"/>
+      <c r="C1531" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1531" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27031,7 +27048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-27 | Publication days: 309</t>
+          <t>Coverage: 2022-01-19 to 2026-03-28 | Publication days: 309</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1531"/>
+  <dimension ref="A1:E1532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27015,6 +27015,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1531" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr"/>
+      <c r="C1532" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1532" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27048,7 +27065,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-28 | Publication days: 309</t>
+          <t>Coverage: 2022-01-19 to 2026-03-29 | Publication days: 309</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1532"/>
+  <dimension ref="A1:E1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27032,6 +27032,23 @@
         <v>-2.733333333333333</v>
       </c>
       <c r="E1532" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr"/>
+      <c r="C1533" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="E1533" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27065,7 +27082,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-29 | Publication days: 309</t>
+          <t>Coverage: 2022-01-19 to 2026-03-30 | Publication days: 309</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1533"/>
+  <dimension ref="A1:E1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27041,15 +27041,36 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B1533" t="inlineStr"/>
+      <c r="B1533" t="n">
+        <v>-2</v>
+      </c>
       <c r="C1533" t="n">
-        <v>-3</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D1533" t="n">
-        <v>-2.733333333333333</v>
+        <v>-2.7</v>
       </c>
       <c r="E1533" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1534" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="E1534" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27082,7 +27103,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-30 | Publication days: 309</t>
+          <t>Coverage: 2022-01-19 to 2026-03-31 | Publication days: 311</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1534"/>
+  <dimension ref="A1:E1535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27071,6 +27071,23 @@
       </c>
       <c r="E1534" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr"/>
+      <c r="C1535" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E1535" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27103,7 +27120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-03-31 | Publication days: 311</t>
+          <t>Coverage: 2022-01-19 to 2026-04-01 | Publication days: 311</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1535"/>
+  <dimension ref="A1:E1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27061,13 +27061,13 @@
         </is>
       </c>
       <c r="B1534" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1534" t="n">
-        <v>-2.428571428571428</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D1534" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27081,13 +27081,32 @@
       </c>
       <c r="B1535" t="inlineStr"/>
       <c r="C1535" t="n">
-        <v>-2</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D1535" t="n">
-        <v>-2.5</v>
+        <v>-2.7</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1536" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>-2.533333333333333</v>
+      </c>
+      <c r="E1536" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27120,7 +27139,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-01 | Publication days: 311</t>
+          <t>Coverage: 2022-01-19 to 2026-04-02 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1536"/>
+  <dimension ref="A1:E1537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27097,16 +27097,33 @@
         </is>
       </c>
       <c r="B1536" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="C1536" t="n">
-        <v>-2.142857142857143</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D1536" t="n">
-        <v>-2.533333333333333</v>
+        <v>-2.7</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr"/>
+      <c r="C1537" t="n">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="D1537" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E1537" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27139,7 +27156,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-02 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-03 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1537"/>
+  <dimension ref="A1:E1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27097,13 +27097,13 @@
         </is>
       </c>
       <c r="B1536" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>-2.857142857142857</v>
+        <v>-2.714285714285714</v>
       </c>
       <c r="D1536" t="n">
-        <v>-2.7</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -27117,12 +27117,29 @@
       </c>
       <c r="B1537" t="inlineStr"/>
       <c r="C1537" t="n">
-        <v>-2.857142857142857</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1537" t="n">
-        <v>-2.7</v>
+        <v>-2.633333333333333</v>
       </c>
       <c r="E1537" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr"/>
+      <c r="C1538" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="E1538" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27156,7 +27173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-03 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-04 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1538"/>
+  <dimension ref="A1:E1539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27140,6 +27140,23 @@
         <v>-2.6</v>
       </c>
       <c r="E1538" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr"/>
+      <c r="C1539" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>-2.566666666666667</v>
+      </c>
+      <c r="E1539" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27173,7 +27190,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-04 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-05 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1539"/>
+  <dimension ref="A1:E1540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27157,6 +27157,23 @@
         <v>-2.566666666666667</v>
       </c>
       <c r="E1539" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr"/>
+      <c r="C1540" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>-2.533333333333333</v>
+      </c>
+      <c r="E1540" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27190,7 +27207,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-05 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-06 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1540"/>
+  <dimension ref="A1:E1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27061,13 +27061,13 @@
         </is>
       </c>
       <c r="B1534" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1534" t="n">
-        <v>-2.857142857142857</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D1534" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="E1534" t="b">
         <v>1</v>
@@ -27081,10 +27081,10 @@
       </c>
       <c r="B1535" t="inlineStr"/>
       <c r="C1535" t="n">
-        <v>-2.857142857142857</v>
+        <v>-2</v>
       </c>
       <c r="D1535" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="E1535" t="b">
         <v>0</v>
@@ -27100,10 +27100,10 @@
         <v>-2</v>
       </c>
       <c r="C1536" t="n">
-        <v>-2.714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D1536" t="n">
-        <v>-2.666666666666667</v>
+        <v>-2.466666666666667</v>
       </c>
       <c r="E1536" t="b">
         <v>1</v>
@@ -27117,10 +27117,10 @@
       </c>
       <c r="B1537" t="inlineStr"/>
       <c r="C1537" t="n">
-        <v>-2.571428571428572</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1537" t="n">
-        <v>-2.633333333333333</v>
+        <v>-2.433333333333333</v>
       </c>
       <c r="E1537" t="b">
         <v>0</v>
@@ -27134,10 +27134,10 @@
       </c>
       <c r="B1538" t="inlineStr"/>
       <c r="C1538" t="n">
-        <v>-2.428571428571428</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1538" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="E1538" t="b">
         <v>0</v>
@@ -27151,10 +27151,10 @@
       </c>
       <c r="B1539" t="inlineStr"/>
       <c r="C1539" t="n">
-        <v>-2.285714285714286</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1539" t="n">
-        <v>-2.566666666666667</v>
+        <v>-2.366666666666667</v>
       </c>
       <c r="E1539" t="b">
         <v>0</v>
@@ -27168,12 +27168,29 @@
       </c>
       <c r="B1540" t="inlineStr"/>
       <c r="C1540" t="n">
-        <v>-2.285714285714286</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1540" t="n">
-        <v>-2.533333333333333</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="E1540" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr"/>
+      <c r="C1541" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E1541" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27207,7 +27224,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-06 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-07 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1541"/>
+  <dimension ref="A1:E1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27191,6 +27191,23 @@
         <v>-2.3</v>
       </c>
       <c r="E1541" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr"/>
+      <c r="C1542" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>-2.266666666666667</v>
+      </c>
+      <c r="E1542" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27224,7 +27241,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-07 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-08 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1542"/>
+  <dimension ref="A1:E1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27208,6 +27208,23 @@
         <v>-2.266666666666667</v>
       </c>
       <c r="E1542" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr"/>
+      <c r="C1543" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>-2.233333333333333</v>
+      </c>
+      <c r="E1543" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27241,7 +27258,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-08 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-09 | Publication days: 312</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1543"/>
+  <dimension ref="A1:E1544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27217,14 +27217,33 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="B1543" t="inlineStr"/>
+      <c r="B1543" t="n">
+        <v>2</v>
+      </c>
       <c r="C1543" t="n">
-        <v>-2</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1543" t="n">
-        <v>-2.233333333333333</v>
+        <v>-2.1</v>
       </c>
       <c r="E1543" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr"/>
+      <c r="C1544" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>-2.133333333333333</v>
+      </c>
+      <c r="E1544" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27258,7 +27277,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-09 | Publication days: 312</t>
+          <t>Coverage: 2022-01-19 to 2026-04-10 | Publication days: 313</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1544"/>
+  <dimension ref="A1:E1545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27244,6 +27244,23 @@
         <v>-2.133333333333333</v>
       </c>
       <c r="E1544" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr"/>
+      <c r="C1545" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>-1.966666666666667</v>
+      </c>
+      <c r="E1545" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27277,7 +27294,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-10 | Publication days: 313</t>
+          <t>Coverage: 2022-01-19 to 2026-04-11 | Publication days: 313</t>
         </is>
       </c>
     </row>

--- a/data/ES.xlsx
+++ b/data/ES.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1545"/>
+  <dimension ref="A1:E1546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27261,6 +27261,23 @@
         <v>-1.966666666666667</v>
       </c>
       <c r="E1545" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr"/>
+      <c r="C1546" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E1546" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27294,7 +27311,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-01-19 to 2026-04-11 | Publication days: 313</t>
+          <t>Coverage: 2022-01-19 to 2026-04-12 | Publication days: 313</t>
         </is>
       </c>
     </row>
